--- a/ig/DM-SIDOBA/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="277">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -506,7 +506,7 @@
     <t>317</t>
   </si>
   <si>
-    <t>Préparateur en pharmacie (officine)</t>
+    <t>Préparateur en pharmacie</t>
   </si>
   <si>
     <t>319</t>
@@ -819,6 +819,30 @@
   </si>
   <si>
     <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>PADHUE - Médecin</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>PADHUE - Pharmacien</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>PADHUE - Sage Femme</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>PADHUE - Chirurgien Dentiste</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -1543,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2120,18 +2144,50 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>118</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="B73" t="s" s="2">
-        <v>268</v>
+      <c r="B77" t="s" s="2">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
